--- a/docs/downloads/05/tbl_cooking_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/05/tbl_cooking_marovoay_ampijoroa.xlsx
@@ -391,7 +391,7 @@
         <v>83</v>
       </c>
       <c r="D2">
-        <v>46.1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -402,14 +402,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C3">
         <v>97</v>
       </c>
       <c r="D3">
-        <v>53.9</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="4">
@@ -427,7 +427,7 @@
         <v>241</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="5">
@@ -438,14 +438,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Morceaux De Bois Résinés</t>
+          <t>Bois de chauffe</t>
         </is>
       </c>
       <c r="C5">
         <v>377</v>
       </c>
       <c r="D5">
-        <v>61</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
   </sheetData>
